--- a/data/trans_orig/P43-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P43-Provincia-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74626</t>
+          <t>76826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>106591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74626</t>
+          <t>76826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>106591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154137</t>
+          <t>154247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186212</t>
+          <t>184012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154137</t>
+          <t>154247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186212</t>
+          <t>184012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162781</t>
+          <t>160732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>203512</t>
+          <t>203427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162781</t>
+          <t>160732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203512</t>
+          <t>203427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>296640</t>
+          <t>296725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337371</t>
+          <t>339420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296640</t>
+          <t>296725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337371</t>
+          <t>339420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117273</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153699</t>
+          <t>153399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117273</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153699</t>
+          <t>153399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179831</t>
+          <t>180131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>216257</t>
+          <t>213554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179831</t>
+          <t>180131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216257</t>
+          <t>213554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133868</t>
+          <t>135238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170833</t>
+          <t>171700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>133868</t>
+          <t>135238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>170833</t>
+          <t>171700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200623</t>
+          <t>199756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237588</t>
+          <t>236218</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200623</t>
+          <t>199756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237588</t>
+          <t>236218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>74351</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>74351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129798</t>
+          <t>130791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156508</t>
+          <t>156856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129798</t>
+          <t>130791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156508</t>
+          <t>156856</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91798</t>
+          <t>91309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123598</t>
+          <t>122832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91798</t>
+          <t>91309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123598</t>
+          <t>122832</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153606</t>
+          <t>154372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185406</t>
+          <t>185895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153606</t>
+          <t>154372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185406</t>
+          <t>185895</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>251764</t>
+          <t>251065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>302755</t>
+          <t>301695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>251764</t>
+          <t>251065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>302755</t>
+          <t>301695</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>331503</t>
+          <t>332563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>382494</t>
+          <t>383193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>331503</t>
+          <t>332563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382494</t>
+          <t>383193</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>239385</t>
+          <t>242245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>294297</t>
+          <t>291791</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>239385</t>
+          <t>242245</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>294297</t>
+          <t>291791</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>482618</t>
+          <t>485124</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>537530</t>
+          <t>534670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>482618</t>
+          <t>485124</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>537530</t>
+          <t>534670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128434</t>
+          <t>129089</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162817</t>
+          <t>162659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128434</t>
+          <t>129089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162817</t>
+          <t>162659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119084</t>
+          <t>119242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153467</t>
+          <t>152812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119084</t>
+          <t>119242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153467</t>
+          <t>152812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195339</t>
+          <t>193969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243894</t>
+          <t>241108</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195339</t>
+          <t>193969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243894</t>
+          <t>241108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278839</t>
+          <t>281625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327394</t>
+          <t>328764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278839</t>
+          <t>281625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327394</t>
+          <t>328764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140698</t>
+          <t>139500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180355</t>
+          <t>178110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140698</t>
+          <t>139500</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180355</t>
+          <t>178110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>161924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199336</t>
+          <t>200534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>161924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>199336</t>
+          <t>200534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>167124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207632</t>
+          <t>207329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>167124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207632</t>
+          <t>207329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179344</t>
+          <t>179647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219600</t>
+          <t>219852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179344</t>
+          <t>179647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219600</t>
+          <t>219852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90099</t>
+          <t>90031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119698</t>
+          <t>119306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90099</t>
+          <t>90031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119698</t>
+          <t>119306</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>100285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129492</t>
+          <t>129560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>100285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129492</t>
+          <t>129560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,0%</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118661</t>
+          <t>118457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153174</t>
+          <t>152846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>118661</t>
+          <t>118457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153174</t>
+          <t>152846</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126857</t>
+          <t>127185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161370</t>
+          <t>161574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126857</t>
+          <t>127185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>161370</t>
+          <t>161574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>327108</t>
+          <t>324685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>381563</t>
+          <t>382315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>327108</t>
+          <t>324685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381563</t>
+          <t>382315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>309256</t>
+          <t>308504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>363711</t>
+          <t>366134</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309256</t>
+          <t>308504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>363711</t>
+          <t>366134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>336745</t>
+          <t>334089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395371</t>
+          <t>392871</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>336745</t>
+          <t>334089</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>395371</t>
+          <t>392871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>419103</t>
+          <t>421603</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>477729</t>
+          <t>480385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>419103</t>
+          <t>421603</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>477729</t>
+          <t>480385</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1607282</t>
+          <t>1611161</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1727835</t>
+          <t>1727789</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1607282</t>
+          <t>1611161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1727835</t>
+          <t>1727789</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1808723</t>
+          <t>1808769</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1929276</t>
+          <t>1925397</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1808723</t>
+          <t>1808769</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1929276</t>
+          <t>1925397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5307,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126115</t>
+          <t>128457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160812</t>
+          <t>162630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126115</t>
+          <t>128457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160812</t>
+          <t>162630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125450</t>
+          <t>123632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160147</t>
+          <t>157805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125450</t>
+          <t>123632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160147</t>
+          <t>157805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>244101</t>
+          <t>243087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>290309</t>
+          <t>286539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244101</t>
+          <t>243087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>290309</t>
+          <t>286539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231152</t>
+          <t>234922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>277360</t>
+          <t>278374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231152</t>
+          <t>234922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277360</t>
+          <t>278374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,38%</t>
         </is>
       </c>
     </row>
@@ -5783,12 +5783,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170485</t>
+          <t>169138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205875</t>
+          <t>205375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170485</t>
+          <t>169138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205875</t>
+          <t>205375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125734</t>
+          <t>126234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161124</t>
+          <t>162471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125734</t>
+          <t>126234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161124</t>
+          <t>162471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181471</t>
+          <t>182957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>224547</t>
+          <t>223623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181471</t>
+          <t>182957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224547</t>
+          <t>223623</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>162455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204607</t>
+          <t>203121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161531</t>
+          <t>162455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204607</t>
+          <t>203121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>101488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128818</t>
+          <t>128626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>101488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128818</t>
+          <t>128626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88901</t>
+          <t>89093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116881</t>
+          <t>116231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88901</t>
+          <t>89093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>116881</t>
+          <t>116231</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -6497,12 +6497,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120525</t>
+          <t>118728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153488</t>
+          <t>151484</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120525</t>
+          <t>118728</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153488</t>
+          <t>151484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6575,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119627</t>
+          <t>121631</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152590</t>
+          <t>154387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119627</t>
+          <t>121631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152590</t>
+          <t>154387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>266166</t>
+          <t>260971</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>313675</t>
+          <t>316616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>266166</t>
+          <t>260971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313675</t>
+          <t>316616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>367709</t>
+          <t>364768</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>415218</t>
+          <t>420413</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367709</t>
+          <t>364768</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>415218</t>
+          <t>420413</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,7%</t>
         </is>
       </c>
     </row>
@@ -6973,12 +6973,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>384295</t>
+          <t>385665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>443503</t>
+          <t>444311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>384295</t>
+          <t>385665</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>443503</t>
+          <t>444311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>378560</t>
+          <t>377752</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>437768</t>
+          <t>436398</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>378560</t>
+          <t>377752</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>437768</t>
+          <t>436398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1698387</t>
+          <t>1697844</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1824187</t>
+          <t>1820096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1698387</t>
+          <t>1697844</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1824187</t>
+          <t>1820096</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1695503</t>
+          <t>1699594</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1821303</t>
+          <t>1821846</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1695503</t>
+          <t>1699594</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1821303</t>
+          <t>1821846</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -7619,32 +7619,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102801</t>
+          <t>106382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127329</t>
+          <t>129764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7654,32 +7654,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102801</t>
+          <t>106382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127329</t>
+          <t>129764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -7697,32 +7697,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70121</t>
+          <t>84999</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58884</t>
+          <t>73990</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83412</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70121</t>
+          <t>84999</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58884</t>
+          <t>73990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83412</t>
+          <t>97372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -7775,17 +7775,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7810,17 +7810,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>222489</t>
+          <t>230743</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203073</t>
+          <t>210906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239428</t>
+          <t>250821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>222489</t>
+          <t>230743</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>203073</t>
+          <t>210906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239428</t>
+          <t>250821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -7935,32 +7935,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>183847</t>
+          <t>199879</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>166908</t>
+          <t>179801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203263</t>
+          <t>219716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7970,32 +7970,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>183847</t>
+          <t>199879</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>166908</t>
+          <t>179801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203263</t>
+          <t>219716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -8013,17 +8013,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>406336</t>
+          <t>430622</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>406336</t>
+          <t>430622</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>406336</t>
+          <t>430622</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8048,17 +8048,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>406336</t>
+          <t>430622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>406336</t>
+          <t>430622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>406336</t>
+          <t>430622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8095,32 +8095,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>135628</t>
+          <t>137858</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122705</t>
+          <t>122995</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148684</t>
+          <t>151838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8130,32 +8130,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135628</t>
+          <t>137858</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122705</t>
+          <t>122995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148684</t>
+          <t>151838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -8173,32 +8173,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116348</t>
+          <t>118371</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103292</t>
+          <t>104391</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129271</t>
+          <t>133234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8208,32 +8208,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>116348</t>
+          <t>118371</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103292</t>
+          <t>104391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129271</t>
+          <t>133234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -8251,17 +8251,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>251976</t>
+          <t>256229</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>251976</t>
+          <t>256229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>251976</t>
+          <t>256229</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8286,17 +8286,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>251976</t>
+          <t>256229</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>251976</t>
+          <t>256229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251976</t>
+          <t>256229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8333,32 +8333,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>182240</t>
+          <t>166721</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102968</t>
+          <t>148907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238161</t>
+          <t>185965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182240</t>
+          <t>166721</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102968</t>
+          <t>148907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238161</t>
+          <t>185965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>57,87%</t>
         </is>
       </c>
     </row>
@@ -8411,32 +8411,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>203797</t>
+          <t>154625</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147876</t>
+          <t>135381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283069</t>
+          <t>172439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8446,32 +8446,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>203797</t>
+          <t>154625</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147876</t>
+          <t>135381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283069</t>
+          <t>172439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -8489,17 +8489,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>386037</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>386037</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>386037</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>386037</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>386037</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>386037</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8571,32 +8571,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102638</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119390</t>
+          <t>129087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8606,32 +8606,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102638</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119390</t>
+          <t>129087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -8649,32 +8649,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34337</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51089</t>
+          <t>58115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8684,32 +8684,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34337</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51089</t>
+          <t>58115</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -8727,17 +8727,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8762,17 +8762,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>168113</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99523</t>
+          <t>103940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123142</t>
+          <t>127394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,32 +8844,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99523</t>
+          <t>103940</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123142</t>
+          <t>127394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,13%</t>
         </is>
       </c>
     </row>
@@ -8887,32 +8887,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>98071</t>
+          <t>100103</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86682</t>
+          <t>88038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110301</t>
+          <t>111492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8922,32 +8922,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>98071</t>
+          <t>100103</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86682</t>
+          <t>88038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110301</t>
+          <t>111492</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -8965,17 +8965,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>209824</t>
+          <t>215432</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9047,32 +9047,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>484922</t>
+          <t>328020</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>400214</t>
+          <t>305427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>581905</t>
+          <t>348865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9082,32 +9082,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>484922</t>
+          <t>328020</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>400214</t>
+          <t>305427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>581905</t>
+          <t>348865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -9125,32 +9125,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>173706</t>
+          <t>208730</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76723</t>
+          <t>187885</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258414</t>
+          <t>231323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9160,32 +9160,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>173706</t>
+          <t>208730</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76723</t>
+          <t>187885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258414</t>
+          <t>231323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -9203,17 +9203,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>658628</t>
+          <t>536750</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>658628</t>
+          <t>536750</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>658628</t>
+          <t>536750</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>658628</t>
+          <t>536750</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>658628</t>
+          <t>536750</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>658628</t>
+          <t>536750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9285,32 +9285,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>218035</t>
+          <t>249226</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>197773</t>
+          <t>229425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>235425</t>
+          <t>272368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9320,32 +9320,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>218035</t>
+          <t>249226</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197773</t>
+          <t>229425</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235425</t>
+          <t>272368</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -9363,32 +9363,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>360182</t>
+          <t>421415</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>342792</t>
+          <t>398273</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>380444</t>
+          <t>441216</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9398,32 +9398,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>360182</t>
+          <t>421415</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>342792</t>
+          <t>398273</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>380444</t>
+          <t>441216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -9441,17 +9441,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9476,17 +9476,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>578217</t>
+          <t>670641</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1445705</t>
+          <t>1418108</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1873457</t>
+          <t>1510341</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1445705</t>
+          <t>1418108</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1873457</t>
+          <t>1510341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1247819</t>
+          <t>1336394</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>957499</t>
+          <t>1292545</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1385251</t>
+          <t>1384778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1247819</t>
+          <t>1336394</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>957499</t>
+          <t>1292545</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1385251</t>
+          <t>1384778</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -9679,17 +9679,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9714,17 +9714,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
